--- a/base/StructureDefinition-SGStructureMap.xlsx
+++ b/base/StructureDefinition-SGStructureMap.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -359,7 +359,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -746,7 +746,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -846,7 +846,7 @@
     <t>StructureMap.structure.url</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -892,7 +892,7 @@
     <t>StructureMap.import</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureMap)
+    <t xml:space="preserve">canonical(StructureMap|4.0.1)
 </t>
   </si>
   <si>
@@ -1664,15 +1664,15 @@
   <dimension ref="A1:AN94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.2734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="56.2734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.05078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="49.05078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1683,26 +1683,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="77.45703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.8359375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.8203125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="47.06640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="68.578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.77734375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="41.2578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.67578125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="43.078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
